--- a/out/Attention-MambaAMT_repeat_2_000007.xlsx
+++ b/out/Attention-MambaAMT_repeat_2_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.5212238253023744</v>
+        <v>3.354107168743696</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.5212238253023744</v>
+        <v>3.354107168743696</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.121223825302375</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-2.686681742285026</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-2.686681742285026</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-2.686681742285026</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.5212238253023744</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>-2.686681742285026</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.2363827036687994</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.5212238253023744</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.5212238253023744</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.5212238253023744</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.5212238253023744</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0001397475441489369</v>
+        <v>-0.0004015327648546081</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>1.611082790147016</v>
+        <v>4.629079677242723</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-2.686681742285026</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC40" t="n">
-        <v>3.224656023537508</v>
+        <v>9.265315227817705</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.2415890283710166</v>
+        <v>0.694151169578656</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.5212238253023744</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC41" t="n">
-        <v>2.094589040848379</v>
+        <v>6.018324876557495</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.3020648934499743</v>
+        <v>0.86791482415725</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.5212238253023744</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC42" t="n">
-        <v>2.457168233602733</v>
+        <v>7.060113591339995</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.4330087549224075</v>
+        <v>1.244151784428717</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.121223825302375</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC43" t="n">
-        <v>3.021291205169319</v>
+        <v>8.680992138790069</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.4632335974858739</v>
+        <v>1.330995619960806</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC44" t="n">
-        <v>3.51478192957308</v>
+        <v>10.09892505265612</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4909335065324223</v>
+        <v>1.410587820312774</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC45" t="n">
-        <v>4.033451874645021</v>
+        <v>11.58920509367857</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.2215498265990964</v>
+        <v>0.6365713822394468</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC46" t="n">
-        <v>3.985208580797916</v>
+        <v>11.45058917770579</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.1069977968085776</v>
+        <v>0.3074355253079487</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC47" t="n">
-        <v>3.977481909779587</v>
+        <v>11.42838835436559</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.05098187754764499</v>
+        <v>0.1464832619754544</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC48" t="n">
-        <v>3.972361609635148</v>
+        <v>11.41367643330077</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.015104831877588</v>
+        <v>0.04340233192742231</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC49" t="n">
-        <v>3.951536197076737</v>
+        <v>11.35384057573282</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.009990057716867463</v>
+        <v>0.0287085435968385</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC50" t="n">
-        <v>3.956404444079269</v>
+        <v>11.36783363054517</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.005110582655544775</v>
+        <v>0.01469332154424463</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC51" t="n">
-        <v>3.956629607284216</v>
+        <v>11.36848994578955</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.002611314895259179</v>
+        <v>0.007513759504690578</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC52" t="n">
-        <v>3.956739618581919</v>
+        <v>11.36881539964874</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0009789503923378822</v>
+        <v>0.002821208280761271</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC53" t="n">
-        <v>3.956083214908898</v>
+        <v>11.36693911779061</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0005312538852180916</v>
+        <v>0.001535286159541811</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC54" t="n">
-        <v>3.95616622415572</v>
+        <v>11.36718697563016</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0002532872339314567</v>
+        <v>0.0007372777738214787</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC55" t="n">
-        <v>3.956141205652625</v>
+        <v>11.36712444553203</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0001544007290244765</v>
+        <v>0.0004545070398421638</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC56" t="n">
-        <v>3.956197583653033</v>
+        <v>11.3672958347411</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>7.837890175632158e-05</v>
+        <v>0.0002348430136941102</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC57" t="n">
-        <v>3.956199893583018</v>
+        <v>11.36731177674677</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>3.596281836219229e-05</v>
+        <v>0.0001118938963018658</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC58" t="n">
-        <v>3.956192358105111</v>
+        <v>11.36729954135859</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>2.058292755525423e-05</v>
+        <v>6.919048991023728e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC59" t="n">
-        <v>3.95619882303163</v>
+        <v>11.36732725690503</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>6.65611277636684e-06</v>
+        <v>2.880272705146384e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC60" t="n">
-        <v>3.956191421768172</v>
+        <v>11.36731550921687</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>1.468457874272584e-07</v>
+        <v>1.044053736228177e-05</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC61" t="n">
-        <v>3.956184915041813</v>
+        <v>11.36730639825521</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-1.662115307266386e-06</v>
+        <v>2.788397616378431e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC62" t="n">
-        <v>3.956180411138857</v>
+        <v>11.36730263917409</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.031182895915095e-06</v>
+        <v>-1.124731583660385e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC63" t="n">
-        <v>3.956174978007388</v>
+        <v>11.36729648258384</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-4.053889915940302e-06</v>
+        <v>-3.107779831880603e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC64" t="n">
-        <v>3.956169931386321</v>
+        <v>11.36729138934171</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0</v>
+        <v>-3.735991635587426e-06</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC65" t="n">
-        <v>3.956170249666537</v>
+        <v>11.36728702436774</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC66" t="n">
-        <v>3.956171340912994</v>
+        <v>11.36728811561419</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-2.086681742285026</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC67" t="n">
-        <v>3.956170651305858</v>
+        <v>11.36728742600706</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC68" t="n">
-        <v>3.95617068161826</v>
+        <v>11.36728745631946</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC69" t="n">
-        <v>3.95617049216575</v>
+        <v>11.36728726686695</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC70" t="n">
-        <v>3.956170545212453</v>
+        <v>11.36728731991365</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC71" t="n">
-        <v>3.956170598259156</v>
+        <v>11.36728737296035</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC72" t="n">
-        <v>3.956170560368653</v>
+        <v>11.36728733506985</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC73" t="n">
-        <v>3.956170431540946</v>
+        <v>11.36728720624215</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC74" t="n">
-        <v>3.956170287557039</v>
+        <v>11.36728706225824</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC75" t="n">
-        <v>3.956170128416931</v>
+        <v>11.36728690311813</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC76" t="n">
-        <v>3.956170181463634</v>
+        <v>11.36728695616483</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC77" t="n">
-        <v>3.956170128416931</v>
+        <v>11.36728690311813</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC78" t="n">
-        <v>3.956170128416931</v>
+        <v>11.36728690311813</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC79" t="n">
-        <v>3.956169946542522</v>
+        <v>11.36728672124372</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC80" t="n">
-        <v>3.95617011326073</v>
+        <v>11.36728688796193</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC81" t="n">
-        <v>3.95617031029134</v>
+        <v>11.36728708499254</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC82" t="n">
-        <v>3.956170151151233</v>
+        <v>11.36728692585243</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC83" t="n">
-        <v>3.956170189041734</v>
+        <v>11.36728696374293</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC84" t="n">
-        <v>3.956170386072344</v>
+        <v>11.36728716077354</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC85" t="n">
-        <v>3.956170363338043</v>
+        <v>11.36728713803924</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC86" t="n">
-        <v>3.956170211776035</v>
+        <v>11.36728698647723</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC87" t="n">
-        <v>3.956170135995031</v>
+        <v>11.36728691069623</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC88" t="n">
-        <v>3.956170234510337</v>
+        <v>11.36728700921153</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC89" t="n">
-        <v>3.956170242088437</v>
+        <v>11.36728701678964</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-2.086681742285026</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC90" t="n">
-        <v>3.956170507321951</v>
+        <v>11.36728728202315</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC91" t="n">
-        <v>3.956170211776035</v>
+        <v>11.36728698647723</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC92" t="n">
-        <v>3.956170454275248</v>
+        <v>11.36728722897645</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-2.086681742285026</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC93" t="n">
-        <v>3.956170537634352</v>
+        <v>11.36728731233555</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC94" t="n">
-        <v>3.956170370916144</v>
+        <v>11.36728714561734</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC95" t="n">
-        <v>3.956170560368653</v>
+        <v>11.36728733506985</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC96" t="n">
-        <v>3.956170211776035</v>
+        <v>11.36728698647723</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC97" t="n">
-        <v>3.956170007167324</v>
+        <v>11.36728678186852</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC98" t="n">
-        <v>3.95617012083883</v>
+        <v>11.36728689554003</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-2.086681742285026</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC99" t="n">
-        <v>3.956170135995031</v>
+        <v>11.36728691069623</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC100" t="n">
-        <v>3.95616990107392</v>
+        <v>11.36728667577512</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC101" t="n">
-        <v>3.956169961698722</v>
+        <v>11.36728673639992</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC102" t="n">
-        <v>3.956169832871015</v>
+        <v>11.36728660757221</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC103" t="n">
-        <v>3.956169969276823</v>
+        <v>11.36728674397802</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC104" t="n">
-        <v>3.956170143573131</v>
+        <v>11.36728691827433</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC105" t="n">
-        <v>3.956170287557039</v>
+        <v>11.36728706225824</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC106" t="n">
-        <v>3.95617012083883</v>
+        <v>11.36728689554003</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC107" t="n">
-        <v>3.95617011326073</v>
+        <v>11.36728688796193</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC108" t="n">
-        <v>3.956169825292915</v>
+        <v>11.36728659999411</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC109" t="n">
-        <v>3.956169840449116</v>
+        <v>11.36728661515031</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC110" t="n">
-        <v>3.956170067792128</v>
+        <v>11.36728684249333</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC111" t="n">
-        <v>3.956170052635927</v>
+        <v>11.36728682733713</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC112" t="n">
-        <v>3.956170158729333</v>
+        <v>11.36728693343053</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC113" t="n">
-        <v>3.956169885917718</v>
+        <v>11.36728666061892</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC114" t="n">
-        <v>3.956169984433023</v>
+        <v>11.36728675913422</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC115" t="n">
-        <v>3.956170135995031</v>
+        <v>11.36728691069623</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC116" t="n">
-        <v>3.956170151151233</v>
+        <v>11.36728692585243</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC117" t="n">
-        <v>3.956170128416931</v>
+        <v>11.36728690311813</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC118" t="n">
-        <v>3.956170211776035</v>
+        <v>11.36728698647723</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC119" t="n">
-        <v>3.95617031029134</v>
+        <v>11.36728708499254</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC120" t="n">
-        <v>3.956170143573131</v>
+        <v>11.36728691827433</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC121" t="n">
-        <v>3.956170128416931</v>
+        <v>11.36728690311813</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC122" t="n">
-        <v>3.956170098104529</v>
+        <v>11.36728687280573</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC123" t="n">
-        <v>3.956170082948329</v>
+        <v>11.36728685764953</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC124" t="n">
-        <v>3.95617012083883</v>
+        <v>11.36728689554003</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC125" t="n">
-        <v>3.956170135995031</v>
+        <v>11.36728691069623</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC126" t="n">
-        <v>3.956170128416931</v>
+        <v>11.36728690311813</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-MambaAMT_repeat_2_000007.xlsx
+++ b/out/Attention-MambaAMT_repeat_2_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.5212238253023744</v>
+        <v>0.523124908778771</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.5212238253023744</v>
+        <v>0.523124908778771</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.01011064952692037</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.9433462078326118</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-2.686681742285026</v>
+        <v>-1.676581766138304</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.9433462078326118</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.9433462078326118</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.2101106495269204</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.2101106495269204</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787711</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787711</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787711</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787711</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.01011064952692037</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.01011064952692037</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.2101106495269204</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.5212238253023744</v>
+        <v>0.523124908778771</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787711</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787711</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787711</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787711</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.01011064952692037</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.2101106495269204</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.2101106495269204</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.5212238253023744</v>
+        <v>0.523124908778771</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.121223825302375</v>
+        <v>0.523124908778771</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787711</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787711</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787711</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787711</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787711</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787711</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.5212238253023744</v>
+        <v>0.7231249087787711</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.5212238253023744</v>
+        <v>0.523124908778771</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.5212238253023744</v>
+        <v>0.523124908778771</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.5212238253023744</v>
+        <v>0.523124908778771</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.5212238253023744</v>
+        <v>0.523124908778771</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.2101106495269204</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0001397475441489369</v>
+        <v>-8.397736020106822e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>1.611082790147016</v>
+        <v>0.9681348608504026</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.2101106495269204</v>
       </c>
       <c r="JC40" t="n">
-        <v>3.224656023537508</v>
+        <v>1.937766435033041</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.2415890283710166</v>
+        <v>0.145176163707255</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.2101106495269204</v>
       </c>
       <c r="JC41" t="n">
-        <v>2.094589040848379</v>
+        <v>1.258684379928881</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.3020648934499743</v>
+        <v>0.1815174419028749</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.5212238253023744</v>
+        <v>0.523124908778771</v>
       </c>
       <c r="JC42" t="n">
-        <v>2.457168233602733</v>
+        <v>1.476566155014614</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.4330087549224075</v>
+        <v>0.2602043921391538</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.121223825302375</v>
+        <v>0.523124908778771</v>
       </c>
       <c r="JC43" t="n">
-        <v>3.021291205169319</v>
+        <v>1.815559935716623</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.4632335974858739</v>
+        <v>0.2783671583588291</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.01011064952692037</v>
       </c>
       <c r="JC44" t="n">
-        <v>3.51478192957308</v>
+        <v>2.11210926066688</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4909335065324223</v>
+        <v>0.2950130803609755</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.2101106495269204</v>
       </c>
       <c r="JC45" t="n">
-        <v>4.033451874645021</v>
+        <v>2.423789327069998</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.2215498265990964</v>
+        <v>0.1331339162851011</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.9433462078326118</v>
       </c>
       <c r="JC46" t="n">
-        <v>3.985208580797916</v>
+        <v>2.394798924581531</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.1069977968085776</v>
+        <v>0.06429695331237606</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.9433462078326118</v>
       </c>
       <c r="JC47" t="n">
-        <v>3.977481909779587</v>
+        <v>2.390155807039942</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.05098187754764499</v>
+        <v>0.03063619690674163</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-2.686681742285026</v>
+        <v>-1.676581766138304</v>
       </c>
       <c r="JC48" t="n">
-        <v>3.972361609635148</v>
+        <v>2.38707889949961</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.015104831877588</v>
+        <v>0.009074704695471969</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.9433462078326118</v>
       </c>
       <c r="JC49" t="n">
-        <v>3.951536197076737</v>
+        <v>2.374562429140719</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.009990057716867463</v>
+        <v>0.006000878112616649</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.9433462078326118</v>
       </c>
       <c r="JC50" t="n">
-        <v>3.956404444079269</v>
+        <v>2.37748592404181</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.005110582655544775</v>
+        <v>0.003068875786867066</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.9433462078326118</v>
       </c>
       <c r="JC51" t="n">
-        <v>3.956629607284216</v>
+        <v>2.377619248344154</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.002611314895259179</v>
+        <v>0.001567406258712904</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.9433462078326118</v>
       </c>
       <c r="JC52" t="n">
-        <v>3.956739618581919</v>
+        <v>2.377683379249303</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0009789503923378822</v>
+        <v>0.0005861271203199122</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.01011064952692037</v>
       </c>
       <c r="JC53" t="n">
-        <v>3.956083214908898</v>
+        <v>2.377286785888429</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0005312538852180916</v>
+        <v>0.0003175773371081135</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787711</v>
       </c>
       <c r="JC54" t="n">
-        <v>3.95616622415572</v>
+        <v>2.377334726835364</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0002532872339314567</v>
+        <v>0.000149972340358874</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787711</v>
       </c>
       <c r="JC55" t="n">
-        <v>3.956141205652625</v>
+        <v>2.377317685421104</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0001544007290244765</v>
+        <v>9.142760150863396e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787711</v>
       </c>
       <c r="JC56" t="n">
-        <v>3.956197583653033</v>
+        <v>2.377349700715512</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>7.837890175632158e-05</v>
+        <v>4.543908871678713e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787711</v>
       </c>
       <c r="JC57" t="n">
-        <v>3.956199893583018</v>
+        <v>2.377349095266226</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>3.596281836219229e-05</v>
+        <v>1.897823513884426e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.01011064952692037</v>
       </c>
       <c r="JC58" t="n">
-        <v>3.956192358105111</v>
+        <v>2.377342580771634</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>2.058292755525423e-05</v>
+        <v>1.034975653315254e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.9433462078326118</v>
       </c>
       <c r="JC59" t="n">
-        <v>3.95619882303163</v>
+        <v>2.377344571883431</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>6.65611277636684e-06</v>
+        <v>1.993667665820105e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.9433462078326118</v>
       </c>
       <c r="JC60" t="n">
-        <v>3.956191421768172</v>
+        <v>2.377338085656754</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>1.468457874272584e-07</v>
+        <v>-1.911892527543644e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.9433462078326118</v>
       </c>
       <c r="JC61" t="n">
-        <v>3.956184915041813</v>
+        <v>2.377332127058616</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-1.662115307266386e-06</v>
+        <v>-2.77474353817759e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.9433462078326118</v>
       </c>
       <c r="JC62" t="n">
-        <v>3.956180411138857</v>
+        <v>2.377327457789979</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.9433462078326118</v>
       </c>
       <c r="JC63" t="n">
-        <v>3.956174978007388</v>
+        <v>2.377322168642416</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-4.053889915940302e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.2101106495269204</v>
       </c>
       <c r="JC64" t="n">
-        <v>3.956169931386321</v>
+        <v>2.377322145908115</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787711</v>
       </c>
       <c r="JC65" t="n">
-        <v>3.956170249666537</v>
+        <v>2.377322464188332</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.01011064952692037</v>
       </c>
       <c r="JC66" t="n">
-        <v>3.956171340912994</v>
+        <v>2.377323555434789</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-2.086681742285026</v>
+        <v>-0.7433462078326117</v>
       </c>
       <c r="JC67" t="n">
-        <v>3.956170651305858</v>
+        <v>2.377322865827653</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.9433462078326118</v>
       </c>
       <c r="JC68" t="n">
-        <v>3.95617068161826</v>
+        <v>2.377322896140055</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.2101106495269204</v>
       </c>
       <c r="JC69" t="n">
-        <v>3.95617049216575</v>
+        <v>2.377322706687544</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787711</v>
       </c>
       <c r="JC70" t="n">
-        <v>3.956170545212453</v>
+        <v>2.377322759734247</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787711</v>
       </c>
       <c r="JC71" t="n">
-        <v>3.956170598259156</v>
+        <v>2.37732281278095</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787711</v>
       </c>
       <c r="JC72" t="n">
-        <v>3.956170560368653</v>
+        <v>2.377322774890448</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.01011064952692037</v>
       </c>
       <c r="JC73" t="n">
-        <v>3.956170431540946</v>
+        <v>2.377322646062741</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.01011064952692037</v>
       </c>
       <c r="JC74" t="n">
-        <v>3.956170287557039</v>
+        <v>2.377322502078834</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.2101106495269204</v>
       </c>
       <c r="JC75" t="n">
-        <v>3.956170128416931</v>
+        <v>2.377322342938725</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.5212238253023744</v>
+        <v>0.7231249087787711</v>
       </c>
       <c r="JC76" t="n">
-        <v>3.956170181463634</v>
+        <v>2.377322395985428</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787711</v>
       </c>
       <c r="JC77" t="n">
-        <v>3.956170128416931</v>
+        <v>2.377322342938725</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787711</v>
       </c>
       <c r="JC78" t="n">
-        <v>3.956170128416931</v>
+        <v>2.377322342938725</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787711</v>
       </c>
       <c r="JC79" t="n">
-        <v>3.956169946542522</v>
+        <v>2.377322161064316</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.01011064952692037</v>
       </c>
       <c r="JC80" t="n">
-        <v>3.95617011326073</v>
+        <v>2.377322327782525</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.2101106495269204</v>
       </c>
       <c r="JC81" t="n">
-        <v>3.95617031029134</v>
+        <v>2.377322524813135</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.2101106495269204</v>
       </c>
       <c r="JC82" t="n">
-        <v>3.956170151151233</v>
+        <v>2.377322365673027</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.2101106495269204</v>
       </c>
       <c r="JC83" t="n">
-        <v>3.956170189041734</v>
+        <v>2.377322403563529</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.9433462078326118</v>
       </c>
       <c r="JC84" t="n">
-        <v>3.956170386072344</v>
+        <v>2.377322600594139</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.9433462078326118</v>
       </c>
       <c r="JC85" t="n">
-        <v>3.956170363338043</v>
+        <v>2.377322577859838</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.2101106495269204</v>
       </c>
       <c r="JC86" t="n">
-        <v>3.956170211776035</v>
+        <v>2.37732242629783</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.5212238253023744</v>
+        <v>0.523124908778771</v>
       </c>
       <c r="JC87" t="n">
-        <v>3.956170135995031</v>
+        <v>2.377322350516826</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787711</v>
       </c>
       <c r="JC88" t="n">
-        <v>3.956170234510337</v>
+        <v>2.377322449032131</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.01011064952692037</v>
       </c>
       <c r="JC89" t="n">
-        <v>3.956170242088437</v>
+        <v>2.377322456610232</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-2.086681742285026</v>
+        <v>-0.01011064952692037</v>
       </c>
       <c r="JC90" t="n">
-        <v>3.956170507321951</v>
+        <v>2.377322721843746</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.2101106495269204</v>
       </c>
       <c r="JC91" t="n">
-        <v>3.956170211776035</v>
+        <v>2.37732242629783</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.2101106495269204</v>
       </c>
       <c r="JC92" t="n">
-        <v>3.956170454275248</v>
+        <v>2.377322668797043</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-2.086681742285026</v>
+        <v>-0.2101106495269204</v>
       </c>
       <c r="JC93" t="n">
-        <v>3.956170537634352</v>
+        <v>2.377322752156147</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.9433462078326118</v>
       </c>
       <c r="JC94" t="n">
-        <v>3.956170370916144</v>
+        <v>2.377322585437938</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.9433462078326118</v>
       </c>
       <c r="JC95" t="n">
-        <v>3.956170560368653</v>
+        <v>2.377322774890448</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.9433462078326118</v>
       </c>
       <c r="JC96" t="n">
-        <v>3.956170211776035</v>
+        <v>2.37732242629783</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.2101106495269204</v>
       </c>
       <c r="JC97" t="n">
-        <v>3.956170007167324</v>
+        <v>2.377322221689119</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.2101106495269204</v>
       </c>
       <c r="JC98" t="n">
-        <v>3.95617012083883</v>
+        <v>2.377322335360625</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-2.086681742285026</v>
+        <v>-0.01011064952692037</v>
       </c>
       <c r="JC99" t="n">
-        <v>3.956170135995031</v>
+        <v>2.377322350516826</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.01011064952692037</v>
       </c>
       <c r="JC100" t="n">
-        <v>3.95616990107392</v>
+        <v>2.377322115595714</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787711</v>
       </c>
       <c r="JC101" t="n">
-        <v>3.956169961698722</v>
+        <v>2.377322176220517</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787711</v>
       </c>
       <c r="JC102" t="n">
-        <v>3.956169832871015</v>
+        <v>2.37732204739281</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787711</v>
       </c>
       <c r="JC103" t="n">
-        <v>3.956169969276823</v>
+        <v>2.377322183798617</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.01011064952692037</v>
       </c>
       <c r="JC104" t="n">
-        <v>3.956170143573131</v>
+        <v>2.377322358094927</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.01011064952692037</v>
       </c>
       <c r="JC105" t="n">
-        <v>3.956170287557039</v>
+        <v>2.377322502078834</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.9433462078326118</v>
       </c>
       <c r="JC106" t="n">
-        <v>3.95617012083883</v>
+        <v>2.377322335360625</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.2101106495269204</v>
       </c>
       <c r="JC107" t="n">
-        <v>3.95617011326073</v>
+        <v>2.377322327782525</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.2101106495269204</v>
       </c>
       <c r="JC108" t="n">
-        <v>3.956169825292915</v>
+        <v>2.37732203981471</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.5212238253023744</v>
+        <v>0.7231249087787711</v>
       </c>
       <c r="JC109" t="n">
-        <v>3.956169840449116</v>
+        <v>2.377322054970911</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787711</v>
       </c>
       <c r="JC110" t="n">
-        <v>3.956170067792128</v>
+        <v>2.377322282313922</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.121223825302375</v>
+        <v>-0.01011064952692037</v>
       </c>
       <c r="JC111" t="n">
-        <v>3.956170052635927</v>
+        <v>2.377322267157722</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.01011064952692037</v>
       </c>
       <c r="JC112" t="n">
-        <v>3.956170158729333</v>
+        <v>2.377322373251127</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.2101106495269204</v>
       </c>
       <c r="JC113" t="n">
-        <v>3.956169885917718</v>
+        <v>2.377322100439513</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.5212238253023744</v>
+        <v>0.7231249087787711</v>
       </c>
       <c r="JC114" t="n">
-        <v>3.956169984433023</v>
+        <v>2.377322198954818</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787711</v>
       </c>
       <c r="JC115" t="n">
-        <v>3.956170135995031</v>
+        <v>2.377322350516826</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787711</v>
       </c>
       <c r="JC116" t="n">
-        <v>3.956170151151233</v>
+        <v>2.377322365673027</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787711</v>
       </c>
       <c r="JC117" t="n">
-        <v>3.956170128416931</v>
+        <v>2.377322342938725</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787711</v>
       </c>
       <c r="JC118" t="n">
-        <v>3.956170211776035</v>
+        <v>2.37732242629783</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787711</v>
       </c>
       <c r="JC119" t="n">
-        <v>3.95617031029134</v>
+        <v>2.377322524813135</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787711</v>
       </c>
       <c r="JC120" t="n">
-        <v>3.956170143573131</v>
+        <v>2.377322358094927</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.121223825302375</v>
+        <v>0.7231249087787711</v>
       </c>
       <c r="JC121" t="n">
-        <v>3.956170128416931</v>
+        <v>2.377322342938725</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.5212238253023744</v>
+        <v>0.7231249087787711</v>
       </c>
       <c r="JC122" t="n">
-        <v>3.956170098104529</v>
+        <v>2.377322312626324</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.5212238253023744</v>
+        <v>0.523124908778771</v>
       </c>
       <c r="JC123" t="n">
-        <v>3.956170082948329</v>
+        <v>2.377322297470123</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.5212238253023744</v>
+        <v>0.523124908778771</v>
       </c>
       <c r="JC124" t="n">
-        <v>3.95617012083883</v>
+        <v>2.377322335360625</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.5212238253023744</v>
+        <v>-0.2101106495269204</v>
       </c>
       <c r="JC125" t="n">
-        <v>3.956170135995031</v>
+        <v>2.377322350516826</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-2.686681742285026</v>
+        <v>-0.5767284286797661</v>
       </c>
       <c r="JC126" t="n">
-        <v>3.956170128416931</v>
+        <v>2.377322342938725</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-MambaAMT_repeat_2_000007.xlsx
+++ b/out/Attention-MambaAMT_repeat_2_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.00478329136967659</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.523124908778771</v>
+        <v>-0.1600000000000002</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.008943621069192886</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.523124908778771</v>
+        <v>-0.3000000000000002</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.01951068267226219</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.01011064952692037</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.007149573415517807</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.9433462078326118</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.00098409503698349</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.676581766138304</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.008925359696149826</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.9433462078326118</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.003105264157056808</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.9433462078326118</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.00538601353764534</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.2101106495269204</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.00943770632147789</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.2101106495269204</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.0005414597690105438</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.7231249087787711</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.006216604262590408</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.7231249087787711</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.008439261466264725</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.7231249087787711</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.01429527625441551</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.7231249087787711</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.001691531389951706</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.01011064952692037</v>
+        <v>0.3</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.003551047295331955</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.01011064952692037</v>
+        <v>0.3</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.00335833802819252</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.2101106495269204</v>
+        <v>0.16</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.01207477226853371</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.523124908778771</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.007584501057863235</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.7231249087787711</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.005017105489969254</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.7231249087787711</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.02250408753752708</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.7231249087787711</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.02326623722910881</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.7231249087787711</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.0251896046102047</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.01011064952692037</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.004018869251012802</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.2101106495269204</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.008993636816740036</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.2101106495269204</v>
+        <v>-0.16</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.01094285026192665</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.523124908778771</v>
+        <v>-0.3</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.009889114648103714</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.523124908778771</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.01267584040760994</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.7231249087787711</v>
+        <v>-0.16</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.03075006231665611</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.7231249087787711</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.007741730660200119</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.7231249087787711</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.01408952102065086</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.7231249087787711</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.01790209487080574</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.7231249087787711</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.003659632056951523</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.7231249087787711</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.01773641631007195</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.7231249087787711</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.0218677781522274</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.523124908778771</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.03829344734549522</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.523124908778771</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.02398320659995079</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.523124908778771</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.0002195984125137329</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.523124908778771</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.02304137870669365</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.2101106495269204</v>
+        <v>-0.3</v>
       </c>
       <c r="JC39" t="n">
-        <v>-8.397736020106822e-05</v>
+        <v>-7.712256331345998e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0.9681348608504026</v>
+        <v>0.889109252280405</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.004611033946275711</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.2101106495269204</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC40" t="n">
-        <v>1.937766435033041</v>
+        <v>1.779592907008404</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.145176163707255</v>
+        <v>0.1333258984963202</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.01252073422074318</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.2101106495269204</v>
+        <v>-0.3</v>
       </c>
       <c r="JC41" t="n">
-        <v>1.258684379928881</v>
+        <v>1.155942144807108</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.1815174419028749</v>
+        <v>0.1667007545622656</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.008134286850690842</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.523124908778771</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC42" t="n">
-        <v>1.476566155014614</v>
+        <v>1.356038928517799</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.2602043921391538</v>
+        <v>0.2389645784281521</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.02350278571248055</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.523124908778771</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC43" t="n">
-        <v>1.815559935716623</v>
+        <v>1.667361733030028</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.2783671583588291</v>
+        <v>0.2556451129256772</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.007425788789987564</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.01011064952692037</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>2.11210926066688</v>
+        <v>1.939704871897068</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2950130803609755</v>
+        <v>0.2709315542955592</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.005854394286870956</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.2101106495269204</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>2.423789327069998</v>
+        <v>2.225943688836998</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1331339162851011</v>
+        <v>0.1222670373213373</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.008941445499658585</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.9433462078326118</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>2.394798924581531</v>
+        <v>2.19931958941948</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.06429695331237606</v>
+        <v>0.05904874746033055</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.01169763877987862</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.9433462078326118</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>2.390155807039942</v>
+        <v>2.19505546025556</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.03063619690674163</v>
+        <v>0.02813558306727647</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.0007626190781593323</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.676581766138304</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>2.38707889949961</v>
+        <v>2.192229698691393</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.009074704695471969</v>
+        <v>0.008333563627179606</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.005096931010484695</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.9433462078326118</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.374562429140719</v>
+        <v>2.180734450292196</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.006000878112616649</v>
+        <v>0.005510641582937633</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.01316766068339348</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.9433462078326118</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>2.37748592404181</v>
+        <v>2.18341892269172</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.003068875786867066</v>
+        <v>0.002817967231921131</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.008560627698898315</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.9433462078326118</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.377619248344154</v>
+        <v>2.183540957973626</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001567406258712904</v>
+        <v>0.001439560167255453</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.006792027503252029</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.9433462078326118</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.377683379249303</v>
+        <v>2.183599447234295</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0005861271203199122</v>
+        <v>0.0005376864856202011</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.0007002986967563629</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.01011064952692037</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.377286785888429</v>
+        <v>2.183234922977324</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0003175773371081135</v>
+        <v>0.0002911771458358382</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.009772855788469315</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.7231249087787711</v>
+        <v>0.3</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.377334726835364</v>
+        <v>2.183278531161338</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.000149972340358874</v>
+        <v>0.0001372566611499408</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.02226201817393303</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.7231249087787711</v>
+        <v>0.3</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.377317685421104</v>
+        <v>2.183262475273386</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>9.142760150863396e-05</v>
+        <v>8.355596056915365e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.01285519823431969</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.7231249087787711</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.377349700715512</v>
+        <v>2.183291468911106</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>4.543908871678713e-05</v>
+        <v>4.132161208684532e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.004856880754232407</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.7231249087787711</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.377349095266226</v>
+        <v>2.183290504722986</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.897823513884426e-05</v>
+        <v>1.698004887727391e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.02537522837519646</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.01011064952692037</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.377342580771634</v>
+        <v>2.183284113910244</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>1.034975653315254e-05</v>
+        <v>9.070610155389825e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.007126901298761368</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.9433462078326118</v>
+        <v>0.16</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.377344571883431</v>
+        <v>2.1832855457952</v>
       </c>
     </row>
     <row r="60">
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.01019283011555672</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.9433462078326118</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.377338085656754</v>
+        <v>2.18327917324003</v>
       </c>
     </row>
     <row r="61">
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.0152796171605587</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.9433462078326118</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.377332127058616</v>
+        <v>2.183273351047698</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-2.77474353817759e-06</v>
+        <v>-3.887371769088796e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.004527255892753601</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.9433462078326118</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.377327457789979</v>
+        <v>2.183268599772485</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.00783132016658783</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.9433462078326118</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.377322168642416</v>
+        <v>2.183263310624922</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.01494810357689857</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.2101106495269204</v>
+        <v>0.3</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.377322145908115</v>
+        <v>2.183263287890621</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.01550896093249321</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.7231249087787711</v>
+        <v>0.3</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.377322464188332</v>
+        <v>2.183263606170838</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.009349610656499863</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.01011064952692037</v>
+        <v>0.3</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.377323555434789</v>
+        <v>2.183264697417295</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.01527224108576775</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.7433462078326117</v>
+        <v>0.16</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.377322865827653</v>
+        <v>2.183264007810159</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.01458461582660675</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.9433462078326118</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.377322896140055</v>
+        <v>2.183264038122561</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.004966136068105698</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.2101106495269204</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.377322706687544</v>
+        <v>2.18326384867005</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.003563221544027328</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.7231249087787711</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.377322759734247</v>
+        <v>2.183263901716753</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.002855900675058365</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.7231249087787711</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.37732281278095</v>
+        <v>2.183263954763456</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.006098221987485886</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.7231249087787711</v>
+        <v>0.3</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.377322774890448</v>
+        <v>2.183263916872954</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.004803929477930069</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.01011064952692037</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.377322646062741</v>
+        <v>2.183263788045247</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.001207876950502396</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.01011064952692037</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.377322502078834</v>
+        <v>2.18326364406134</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.005204465240240097</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.2101106495269204</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.377322342938725</v>
+        <v>2.183263484921231</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.006800021976232529</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.7231249087787711</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.377322395985428</v>
+        <v>2.183263537967934</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.008471284061670303</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.7231249087787711</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.377322342938725</v>
+        <v>2.183263484921231</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.01189341023564339</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.7231249087787711</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.377322342938725</v>
+        <v>2.183263484921231</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.01884762570261955</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.7231249087787711</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.377322161064316</v>
+        <v>2.183263303046822</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.01996568217873573</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.01011064952692037</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.377322327782525</v>
+        <v>2.183263469765031</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.005011670291423798</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.2101106495269204</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.377322524813135</v>
+        <v>2.183263666795641</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.01163477823138237</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.2101106495269204</v>
+        <v>-0.16</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.377322365673027</v>
+        <v>2.183263507655533</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.02027306333184242</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.2101106495269204</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.377322403563529</v>
+        <v>2.183263545546035</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.003286618739366531</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.9433462078326118</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.377322600594139</v>
+        <v>2.183263742576645</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.006355259567499161</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.9433462078326118</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.377322577859838</v>
+        <v>2.183263719842344</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.008151452988386154</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.2101106495269204</v>
+        <v>-0.3</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.37732242629783</v>
+        <v>2.183263568280336</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.01606197282671928</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.523124908778771</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.377322350516826</v>
+        <v>2.183263492499332</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.01025665178894997</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.7231249087787711</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.377322449032131</v>
+        <v>2.183263591014637</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.01303909346461296</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.01011064952692037</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.377322456610232</v>
+        <v>2.183263598592738</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.006639685481786728</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.01011064952692037</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.377322721843746</v>
+        <v>2.183263863826252</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.01467550173401833</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.2101106495269204</v>
+        <v>0.3</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.37732242629783</v>
+        <v>2.183263568280336</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.00825757160782814</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.2101106495269204</v>
+        <v>-0.3</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.377322668797043</v>
+        <v>2.183263810779549</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.002778779715299606</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.2101106495269204</v>
+        <v>-0.3</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.377322752156147</v>
+        <v>2.183263894138653</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.01769375428557396</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.9433462078326118</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.377322585437938</v>
+        <v>2.183263727420444</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.007449422031641006</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.9433462078326118</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.377322774890448</v>
+        <v>2.183263916872954</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.009260188788175583</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.9433462078326118</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.37732242629783</v>
+        <v>2.183263568280336</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.01002131029963493</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.2101106495269204</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.377322221689119</v>
+        <v>2.183263363671625</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.008617009967565536</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.2101106495269204</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.377322335360625</v>
+        <v>2.183263477343131</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.002344969660043716</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.01011064952692037</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.377322350516826</v>
+        <v>2.183263492499332</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.003238260746002197</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.01011064952692037</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.377322115595714</v>
+        <v>2.18326325757822</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.00068708136677742</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.7231249087787711</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.377322176220517</v>
+        <v>2.183263318203023</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.01737220957875252</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.7231249087787711</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.37732204739281</v>
+        <v>2.183263189375316</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.02412661537528038</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.7231249087787711</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.377322183798617</v>
+        <v>2.183263325781123</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.009702075272798538</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.01011064952692037</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.377322358094927</v>
+        <v>2.183263500077433</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-9.578093886375427e-05</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.01011064952692037</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.377322502078834</v>
+        <v>2.18326364406134</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.01340812817215919</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.9433462078326118</v>
+        <v>0.3</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.377322335360625</v>
+        <v>2.183263477343131</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.008412938565015793</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.2101106495269204</v>
+        <v>0.3</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.377322327782525</v>
+        <v>2.183263469765031</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.006386201828718185</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.2101106495269204</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.37732203981471</v>
+        <v>2.183263181797216</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.02591132000088692</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.7231249087787711</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.377322054970911</v>
+        <v>2.183263196953417</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.007317613810300827</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.7231249087787711</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.377322282313922</v>
+        <v>2.183263424296428</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.01970529183745384</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.01011064952692037</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.377322267157722</v>
+        <v>2.183263409140228</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.004095423966646194</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.01011064952692037</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.377322373251127</v>
+        <v>2.183263515233633</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.01252410188317299</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.2101106495269204</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.377322100439513</v>
+        <v>2.183263242422019</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.01920349523425102</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.7231249087787711</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.377322198954818</v>
+        <v>2.183263340937324</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.01009489223361015</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.7231249087787711</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.377322350516826</v>
+        <v>2.183263492499332</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.00941859558224678</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.7231249087787711</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.377322365673027</v>
+        <v>2.183263507655533</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.01442194357514381</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.7231249087787711</v>
+        <v>-0.16</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.377322342938725</v>
+        <v>2.183263484921231</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.01238664612174034</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.7231249087787711</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.37732242629783</v>
+        <v>2.183263568280336</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.001240041106939316</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.7231249087787711</v>
+        <v>-0.3</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.377322524813135</v>
+        <v>2.183263666795641</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.00453520193696022</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.7231249087787711</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.377322358094927</v>
+        <v>2.183263500077433</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.009537722915410995</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.7231249087787711</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.377322342938725</v>
+        <v>2.183263484921231</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.006275679916143417</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.7231249087787711</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.377322312626324</v>
+        <v>2.18326345460883</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.01025937870144844</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.523124908778771</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.377322297470123</v>
+        <v>2.183263439452629</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.004112232476472855</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.523124908778771</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.377322335360625</v>
+        <v>2.183263477343131</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.005873102694749832</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.2101106495269204</v>
+        <v>-0.9299999999999997</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.377322350516826</v>
+        <v>2.183263492499332</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.001150142401456833</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.5767284286797661</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.377322342938725</v>
+        <v>2.183263484921231</v>
       </c>
     </row>
   </sheetData>
